--- a/simulacaoes_/custo_robustez_C13/simulacao_rho025/design_variables_statistics.xlsx
+++ b/simulacaoes_/custo_robustez_C13/simulacao_rho025/design_variables_statistics.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,57 +417,57 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Variável</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Desvio padrão</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>CV (%)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Mínimo</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>1º quartil</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Mediana</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>3º quartil</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Máximo</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Amplitude</t>
         </is>
@@ -495,31 +483,31 @@
         <v>50</v>
       </c>
       <c r="C2" t="n">
-        <v>68.22</v>
+        <v>67.37</v>
       </c>
       <c r="D2" t="n">
-        <v>17.2</v>
+        <v>16.25</v>
       </c>
       <c r="E2" t="n">
-        <v>25.22</v>
+        <v>24.12</v>
       </c>
       <c r="F2" t="n">
-        <v>45.55</v>
+        <v>46.66</v>
       </c>
       <c r="G2" t="n">
-        <v>51.99</v>
+        <v>52.2</v>
       </c>
       <c r="H2" t="n">
-        <v>65.45</v>
+        <v>64.06999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>82.34</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="J2" t="n">
         <v>100</v>
       </c>
       <c r="K2" t="n">
-        <v>54.45</v>
+        <v>53.34</v>
       </c>
     </row>
     <row r="3">
@@ -532,31 +520,31 @@
         <v>50</v>
       </c>
       <c r="C3" t="n">
-        <v>45.52</v>
+        <v>45.7</v>
       </c>
       <c r="D3" t="n">
-        <v>0.97</v>
+        <v>0.44</v>
       </c>
       <c r="E3" t="n">
-        <v>2.13</v>
+        <v>0.96</v>
       </c>
       <c r="F3" t="n">
-        <v>41.53</v>
+        <v>45.5</v>
       </c>
       <c r="G3" t="n">
-        <v>45.62</v>
+        <v>45.5</v>
       </c>
       <c r="H3" t="n">
-        <v>45.63</v>
+        <v>45.51</v>
       </c>
       <c r="I3" t="n">
-        <v>45.76</v>
+        <v>45.61</v>
       </c>
       <c r="J3" t="n">
-        <v>47.56</v>
+        <v>47.72</v>
       </c>
       <c r="K3" t="n">
-        <v>6.03</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="4">
@@ -569,31 +557,31 @@
         <v>50</v>
       </c>
       <c r="C4" t="n">
-        <v>8.859999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="E4" t="n">
-        <v>17.75</v>
+        <v>18.19</v>
       </c>
       <c r="F4" t="n">
-        <v>6.3</v>
+        <v>6.63</v>
       </c>
       <c r="G4" t="n">
         <v>7.51</v>
       </c>
       <c r="H4" t="n">
-        <v>8.59</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>10.34</v>
+        <v>10.86</v>
       </c>
       <c r="J4" t="n">
-        <v>11.22</v>
+        <v>11.51</v>
       </c>
       <c r="K4" t="n">
-        <v>4.92</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="5">
@@ -606,31 +594,31 @@
         <v>50</v>
       </c>
       <c r="C5" t="n">
-        <v>115.09</v>
+        <v>116.69</v>
       </c>
       <c r="D5" t="n">
-        <v>27.37</v>
+        <v>28.82</v>
       </c>
       <c r="E5" t="n">
-        <v>23.78</v>
+        <v>24.7</v>
       </c>
       <c r="F5" t="n">
-        <v>80.87</v>
+        <v>75.89</v>
       </c>
       <c r="G5" t="n">
-        <v>92.48999999999999</v>
+        <v>103.03</v>
       </c>
       <c r="H5" t="n">
-        <v>109.34</v>
+        <v>110.39</v>
       </c>
       <c r="I5" t="n">
-        <v>129.46</v>
+        <v>123.03</v>
       </c>
       <c r="J5" t="n">
-        <v>169.59</v>
+        <v>188.68</v>
       </c>
       <c r="K5" t="n">
-        <v>88.72</v>
+        <v>112.8</v>
       </c>
     </row>
     <row r="6">
@@ -643,31 +631,31 @@
         <v>50</v>
       </c>
       <c r="C6" t="n">
-        <v>2.41</v>
+        <v>3.1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.28</v>
+        <v>0.63</v>
       </c>
       <c r="E6" t="n">
-        <v>11.59</v>
+        <v>20.32</v>
       </c>
       <c r="F6" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G6" t="n">
-        <v>2.16</v>
+        <v>2.4</v>
       </c>
       <c r="H6" t="n">
-        <v>2.45</v>
+        <v>3.37</v>
       </c>
       <c r="I6" t="n">
-        <v>2.59</v>
+        <v>3.42</v>
       </c>
       <c r="J6" t="n">
-        <v>3.07</v>
+        <v>4.13</v>
       </c>
       <c r="K6" t="n">
-        <v>1.06</v>
+        <v>2.09</v>
       </c>
     </row>
   </sheetData>
